--- a/output/pdf_financials_xlsx/SURG.xlsx
+++ b/output/pdf_financials_xlsx/SURG.xlsx
@@ -496,20 +496,14 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -540,20 +534,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.093801</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.146718</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>0.11735</v>
       </c>
     </row>
     <row r="8">
@@ -562,20 +550,14 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -584,20 +566,14 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -606,20 +582,14 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>-1.805317</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-2.400157</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>-2.503239</v>
       </c>
     </row>
     <row r="11">
@@ -650,20 +620,14 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -672,20 +636,14 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -694,20 +652,14 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -716,20 +668,14 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -760,20 +706,14 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -848,20 +788,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -870,20 +804,14 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1002,20 +930,14 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1142,15 +1064,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1164,15 +1082,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0.084658</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>1.881003</v>
       </c>
     </row>
     <row r="37">
@@ -1186,15 +1100,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1208,15 +1118,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1230,15 +1136,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1253,10 +1155,10 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0.0044</v>
+        <v>0.018136</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0.00378</v>
+        <v>0.233393</v>
       </c>
     </row>
     <row r="41">
@@ -1270,15 +1172,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0.018136</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.233393</v>
       </c>
     </row>
     <row r="42">
@@ -1292,15 +1190,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1314,15 +1208,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1336,15 +1226,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1358,15 +1244,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1380,15 +1262,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1402,15 +1280,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1424,15 +1298,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0.08805200000000001</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0.083009</v>
       </c>
     </row>
     <row r="49">
@@ -1464,15 +1334,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1486,15 +1352,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1508,15 +1370,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1530,15 +1388,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1552,15 +1406,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1596,15 +1446,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1618,15 +1464,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1640,15 +1482,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>51.125287</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>54.800577</v>
       </c>
     </row>
     <row r="59">
@@ -1662,15 +1500,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1684,15 +1518,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1706,15 +1536,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0.024711</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0.018892</v>
       </c>
     </row>
     <row r="62">
@@ -1782,15 +1608,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1804,15 +1626,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1826,15 +1644,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1848,15 +1662,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="3" t="n">
+        <v>0.507694</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.334473</v>
       </c>
     </row>
     <row r="69">
@@ -1870,15 +1680,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1892,15 +1698,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1914,15 +1716,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1936,15 +1734,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1958,15 +1752,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1980,15 +1770,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2002,15 +1788,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0.342856</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.07688300000000001</v>
       </c>
     </row>
     <row r="76">
@@ -2042,15 +1824,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2064,15 +1842,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2086,15 +1860,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2130,15 +1900,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2152,15 +1918,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2174,15 +1936,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2196,15 +1954,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2218,15 +1972,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>4.062634</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>4.162372</v>
       </c>
     </row>
     <row r="86">
@@ -2276,15 +2026,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>66.465142</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>74.060417</v>
       </c>
     </row>
     <row r="89">
@@ -2298,15 +2044,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2342,15 +2084,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2382,15 +2120,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2422,15 +2156,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2444,15 +2174,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>46.42766</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>52.443146</v>
       </c>
     </row>
     <row r="97">
@@ -2508,20 +2234,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2530,20 +2250,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2552,20 +2266,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2574,20 +2282,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0.016269</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>-0.031919</v>
       </c>
     </row>
     <row r="104">
@@ -2596,20 +2298,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -2618,20 +2314,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2640,20 +2330,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.016269</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>-0.031919</v>
       </c>
     </row>
     <row r="107">
@@ -2662,20 +2346,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.972862</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>1.010176</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0.998395</v>
       </c>
     </row>
     <row r="108">
@@ -2684,20 +2362,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2706,20 +2378,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2728,20 +2394,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2750,20 +2410,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2772,20 +2426,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2794,20 +2442,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2816,20 +2458,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2838,20 +2474,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2860,20 +2490,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2882,20 +2506,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2904,20 +2522,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2948,20 +2560,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2970,20 +2576,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2992,20 +2592,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3014,20 +2608,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3036,20 +2624,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3058,20 +2640,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3080,20 +2656,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3124,20 +2694,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3162,20 +2726,14 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>2.821995</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.084658</v>
+      </c>
+      <c r="D130" s="3" t="n">
+        <v>1.881003</v>
       </c>
     </row>
     <row r="131">
@@ -3184,20 +2742,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3206,20 +2758,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.168916</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>7.314428</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>10.256619</v>
       </c>
     </row>
     <row r="133">
@@ -3228,20 +2774,14 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>2.990911</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>7.399086</v>
+      </c>
+      <c r="D133" s="3" t="n">
+        <v>12.137622</v>
       </c>
     </row>
     <row r="134">
@@ -3250,20 +2790,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3299,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G232"/>
+  <dimension ref="A1:G128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3421,7 +2955,11 @@
           <t>GST receivable 339,411</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -3557,7 +3095,11 @@
           <t>Exploration and evaluation costs 5,6 61,236,053</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>-</t>
@@ -3588,7 +3130,11 @@
           <t>Right-of-use asset 20,341</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>-</t>
@@ -4248,7 +3794,11 @@
           <t>GST receivable 200,293</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
           <t>-</t>
@@ -4384,7 +3934,11 @@
           <t>Exploration and evaluation costs 5,6 54,456,281</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -4415,7 +3969,11 @@
           <t>Right-of-use asset 47,464</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -5104,7 +4662,11 @@
           <t>Share-based payments 292,705 338,615</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -5130,14 +4692,12 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>(770,637) (527,642)</t>
+          <t>Items not affecting cash total</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>-0.755667</v>
       </c>
       <c r="F56" s="5" t="n">
         <v>-1.261028</v>
@@ -5220,7 +4780,11 @@
           <t>Prepaid expenses 49,552 50,793</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -5543,7 +5107,11 @@
           <t>BEGINNING OF THE PERIOD 8,185,511 3,676,936</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -5692,7 +5260,11 @@
           <t>Share-based payments 338,615 324,958</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>0.972862</v>
       </c>
@@ -5713,20 +5285,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(527,642) (316,874)</t>
+          <t>Taxes recoverable (31,666) (19,429)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>-0.755667</v>
+        <v>-0.059097</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-1.261028</v>
+        <v>-0.186557</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -5747,15 +5319,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Taxes recoverable (31,666) (19,429)</t>
+          <t>Other receivables (3,780) -</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>-0.059097</v>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.186557</v>
+        <v>-0.00442</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -5776,17 +5350,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Other receivables (3,780) -</t>
+          <t>Prepaid expenses 50,793 (18,571)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E78" s="5" t="n">
+        <v>0.007412</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.00442</v>
+        <v>0.016269</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -5807,15 +5379,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Prepaid expenses 50,793 (18,571)</t>
+          <t>Trade and other payables (63,860) 45,488</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>0.007412</v>
+        <v>0.065762</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.016269</v>
+        <v>0.028921</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -5836,15 +5408,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Trade and other payables (63,860) 45,488</t>
+          <t>Lease liability (7,184) (5,792)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>0.065762</v>
+        <v>-0.017375</v>
       </c>
       <c r="F80" s="5" t="n">
-        <v>0.028921</v>
+        <v>-0.02155</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -5865,15 +5437,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lease liability (7,184) (5,792)</t>
+          <t>Cash used in operating activities (583,339) (315,178)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>-0.017375</v>
+        <v>-0.758965</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>-0.02155</v>
+        <v>-1.428365</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -5889,20 +5461,20 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cash used in operating activities (583,339) (315,178)</t>
+          <t>Investment in exploration and evaluation assets (521,676) (185,844)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" s="5" t="n">
-        <v>-0.758965</v>
+        <v>-1.951175</v>
       </c>
       <c r="F82" s="5" t="n">
-        <v>-1.428365</v>
+        <v>-3.3988</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -5923,15 +5495,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Investment in exploration and evaluation assets (521,676) (185,844)</t>
+          <t>Property acquisition costs - -</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>-1.951175</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>-3.3988</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -5952,19 +5528,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Property acquisition costs - -</t>
+          <t>Cash used in investing activities (521,676) (185,844)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E84" s="5" t="n">
+        <v>-1.951175</v>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-3.3988</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -5980,20 +5552,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cash used in investing activities (521,676) (185,844)</t>
+          <t>NET INCREASE IN CASH (1,105,015) (501,022)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>-1.951175</v>
+        <v>-2.541224</v>
       </c>
       <c r="F85" s="5" t="n">
-        <v>-3.3988</v>
+        <v>2.487263</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -6009,20 +5581,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>CASH AND CASH EQUIVALENTS –</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NET INCREASE IN CASH (1,105,015) (501,022)</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>BEGINNING OF THE PERIOD 3,676,936 781,793</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
-        <v>-2.541224</v>
+        <v>2.821995</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>2.487263</v>
+        <v>0.084658</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -6038,20 +5614,20 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS –</t>
+          <t>CASH AND CASH EQUIVALENTS – END</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BEGINNING OF THE PERIOD 3,676,936 781,793</t>
+          <t>OF THE PERIOD $ 2,571,921 $ 280,771 $</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" s="5" t="n">
-        <v>2.821995</v>
+        <v>0.280771</v>
       </c>
       <c r="F87" s="5" t="n">
-        <v>0.084658</v>
+        <v>2.571921</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -6062,30 +5638,34 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CASH AND CASH EQUIVALENTS – END</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OF THE PERIOD $ 2,571,921 $ 280,771 $</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.280771</v>
+          <t>Amortization (Note 7 and 8) $ 7,878 $ 8,235 $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>2.571921</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.024705</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.023635</v>
       </c>
     </row>
     <row r="89">
@@ -6094,10 +5674,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>As at December 31, As at March</t>
+          <t>Consulting 28,529 25,000</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
@@ -6107,10 +5691,10 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.092279</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.07052899999999999</v>
       </c>
     </row>
     <row r="90">
@@ -6121,12 +5705,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents 14 $ 4,295,620 $</t>
+          <t>Management and personnel (Note 10) 534,670 463,671</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -6135,13 +5719,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F90" s="5" t="n">
+        <v>0.743267</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>1.881003</v>
+        <v>0.839802</v>
       </c>
     </row>
     <row r="91">
@@ -6152,12 +5734,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>GST receivable 339,411</t>
+          <t>Marketing and conferences 116,783 23,646</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
@@ -6166,13 +5748,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F91" s="5" t="n">
+        <v>0.121995</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.229613</v>
+        <v>0.257412</v>
       </c>
     </row>
     <row r="92">
@@ -6183,12 +5763,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Other receivable 10 2,520</t>
+          <t>Office 29,883 20,381</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
@@ -6197,13 +5777,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F92" s="5" t="n">
+        <v>0.068227</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.00378</v>
+        <v>0.092545</v>
       </c>
     </row>
     <row r="93">
@@ -6214,27 +5792,29 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Prepaid expenses 114,928</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
+          <t>Professional fees 56,101 6,500</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F93" s="5" t="n">
+        <v>0.19279</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.083009</v>
+        <v>0.103571</v>
       </c>
     </row>
     <row r="94">
@@ -6245,12 +5825,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Total Current Assets 4,752,479</t>
+          <t>Share based payments 292,705 338,615</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -6259,13 +5839,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F94" s="5" t="n">
+        <v>1.010176</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>2.197405</v>
+        <v>0.998395</v>
       </c>
     </row>
     <row r="95">
@@ -6276,27 +5854,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs 5,6 61,236,053</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
+          <t>Shareholder communications 1,909 1,600</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F95" s="5" t="n">
+        <v>0.01093</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>54.759893</v>
+        <v>0.011369</v>
       </c>
     </row>
     <row r="96">
@@ -6307,27 +5887,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Right-of-use asset 20,341</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
+          <t>Transfer agent and filing fees 11,134 10,356</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F96" s="5" t="n">
+        <v>0.03605</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.040684</v>
+        <v>0.038523</v>
       </c>
     </row>
     <row r="97">
@@ -6338,27 +5920,29 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Equipment and camp buildings 7 15,600</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
+          <t>Travel 29,005 5,470</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F97" s="5" t="n">
+        <v>0.09973799999999999</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.018892</v>
+        <v>0.067458</v>
       </c>
     </row>
     <row r="98">
@@ -6369,27 +5953,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Total Non-Current Assets 61,271,994</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="n">
+        <v>-1.805317</v>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>-2.400157</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>54.819469</v>
+        <v>-2.503239</v>
       </c>
     </row>
     <row r="99">
@@ -6400,12 +5984,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Total Assets $ 66,024,473 $</t>
+          <t>Interest expense (91) (1,843)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
@@ -6414,13 +5998,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>-0.005528</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>57.016874</v>
+        <v>-0.003776</v>
       </c>
     </row>
     <row r="100">
@@ -6431,27 +6013,29 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Trade and other payables 9 $ 543,065 $</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Interest income 33,868 24,225</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F100" s="5" t="n">
+        <v>0.08909400000000001</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.334473</v>
+        <v>0.063891</v>
       </c>
     </row>
     <row r="101">
@@ -6462,27 +6046,25 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Current portion of lease liability 8 27,951</t>
+          <t>Miscellaneous income - -</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>0.033262</v>
+      <c r="E101" s="5" t="n">
+        <v>0.000135</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.000882</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="102">
@@ -6493,12 +6075,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Deferred compensation liability 10,11 1,370,904</t>
+          <t>Rental income 3600 6,600</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -6507,13 +6089,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F102" s="5" t="n">
+        <v>0.0198</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.043621</v>
+        <v>0.0108</v>
       </c>
     </row>
     <row r="103">
@@ -6524,12 +6104,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Total Current Liabilities 1,941,920</t>
+          <t>Loss on revaluation of deferred compensation liability (752,117) -</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
@@ -6544,7 +6124,7 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.411356</v>
+        <v>-0.986837</v>
       </c>
     </row>
     <row r="104">
@@ -6555,27 +6135,23 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Lease obligation liability 8 -</t>
+          <t>Other income realization of flow-through premium liability - 66,590</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E104" s="5" t="n">
+        <v>1.376199</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>1.376199</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.018372</v>
+        <v>0.849057</v>
       </c>
     </row>
     <row r="105">
@@ -6586,12 +6162,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Deferred income tax liability 4,144,000</t>
+          <t>LOSS BEFORE INCOME TAXES (1,823,337) (874,492)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -6600,13 +6176,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F105" s="5" t="n">
+        <v>-1.129953</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>4.144</v>
+        <v>-2.570104</v>
       </c>
     </row>
     <row r="106">
@@ -6617,15 +6191,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Total Non-Current Liabilities 4,144,000</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>INCOME TAXES - -</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -6636,8 +6214,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" s="5" t="n">
-        <v>4.162372</v>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="107">
@@ -6648,12 +6228,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Total Liabilities 6,085,920</t>
+          <t>LOSS FOR THE PERIOD $ (1,823,337) $ (874,492) $</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
@@ -6662,13 +6242,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F107" s="5" t="n">
+        <v>-1.129953</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>4.573728</v>
+        <v>-2.570104</v>
       </c>
     </row>
     <row r="108">
@@ -6679,12 +6257,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Share capital 11 83,467,979</t>
+          <t>LOSS PER SHARE - BASIC $ (0.005) $ (0.00) $</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -6693,13 +6271,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F108" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>74.060417</v>
+        <v>-7e-09</v>
       </c>
     </row>
     <row r="109">
@@ -6710,12 +6286,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Contributed surplus 11 14,188,787</t>
+          <t>LOSS PER SHARE – DILUTED $ (0.005) $ (0.00) $</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -6724,13 +6300,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F109" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>13.530838</v>
+        <v>-7e-09</v>
       </c>
     </row>
     <row r="110">
@@ -6741,27 +6315,29 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>WEIGHTED AVERAGE NUMBER OF</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Deficit (37,718,213)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
+          <t>COMMON SHARES OUTSTANDING 326,225,863 287,958,552</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F110" s="5" t="n">
+        <v>277.097878</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-35.148109</v>
+        <v>326.225863</v>
       </c>
     </row>
     <row r="111">
@@ -6772,27 +6348,29 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Total Shareholders' Equity 59,938,553</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>52.443146</v>
+          <t>Amortization (Note 7 and 8) $ 8,235 $ 9,016 $</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>0.02705</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>0.024705</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="112">
@@ -6803,27 +6381,25 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Total Liabilities and Shareholders' Equity $ 66,024,473 $</t>
+          <t>Consulting 25,000 5,000</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>57.016874</v>
+      <c r="E112" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.092279</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="113">
@@ -6834,25 +6410,25 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Corporate information and nature of operations</t>
+          <t>Management and personnel (Note 10) 463,671 136,071</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E113" s="5" t="n">
+        <v>0.419753</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.743267</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="114">
@@ -6863,25 +6439,25 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>SHAREHOLDERS' EQUITY</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Subsequent events</t>
+          <t>Marketing and conferences 23,646 40,143</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E114" s="5" t="n">
+        <v>0.103433</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>1.6e-05</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>1.6e-05</v>
+        <v>0.121995</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="115">
@@ -6892,27 +6468,25 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>"Jim Pettit" Director</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>For the Three and Nine Months Ended December 31, 2025 and</t>
+          <t>Office 20,381 26,697</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>0.002024</v>
+      <c r="E115" s="5" t="n">
+        <v>0.061371</v>
+      </c>
+      <c r="F115" s="5" t="n">
+        <v>0.068227</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="116">
@@ -6923,25 +6497,29 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>"Jim Pettit" Director</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>December 31, December</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Professional fees 6,500 89,548</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.097048</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.19279</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="117">
@@ -6952,27 +6530,25 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>"Jim Pettit" Director</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2025 2024 2025</t>
+          <t>Share based payments 338,615 324,958</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G117" s="5" t="n">
-        <v>0.002024</v>
+      <c r="E117" s="5" t="n">
+        <v>0.972861</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>1.010176</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="118">
@@ -6988,26 +6564,24 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Amortization (Note 7 and 8) $ 7,878 $ 8,235 $ 23,635 $</t>
+          <t>Shareholder communications 1,600 11,147</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G118" s="5" t="n">
-        <v>0.024705</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="n">
+        <v>0.023392</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.01093</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="119">
@@ -7023,22 +6597,24 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Consulting 28,529 25,000 70,529</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>0.092279</v>
+          <t>Transfer agent and filing fees 10,356 13,940</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.04562</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.03605</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="120">
@@ -7054,22 +6630,24 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Management and personnel (Note 10) 534,670 463,671 839,802</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.743267</v>
+          <t>Travel 5,470 574</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.024789</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.09973799999999999</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -7080,27 +6658,25 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Marketing and conferences 116,783 23,646 257,412</t>
+          <t>Interest expense (1,843) (2,853)</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G121" s="5" t="n">
-        <v>0.121995</v>
+      <c r="E121" s="5" t="n">
+        <v>-0.008559000000000001</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>-0.005528</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="122">
@@ -7111,27 +6687,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Office 29,883 20,381 92,545</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G122" s="5" t="n">
-        <v>0.068227</v>
+          <t>Interest income 24,225 2,499</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.038362</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.08909400000000001</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="123">
@@ -7142,31 +6720,25 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Professional fees 56,101 6,500 103,571</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G123" s="5" t="n">
-        <v>0.19279</v>
+          <t>Rental income 6,600 6,600</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" s="5" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.0198</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="124">
@@ -7177,27 +6749,25 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER INCOME (EXPENSE)</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Share based payments 292,705 338,615 998,395</t>
+          <t>LOSS BEFORE INCOME TAXES (874,492) (584,258)</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" s="5" t="n">
-        <v>1.010176</v>
+      <c r="E124" s="5" t="n">
+        <v>-0.9910679999999999</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>-1.129953</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="125">
@@ -7208,27 +6778,25 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shareholder communications 1,909 1,600 11,369</t>
+          <t>LOSS FOR THE PERIOD $ (874,492) $ (584,258) $</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" s="5" t="n">
-        <v>0.01093</v>
+      <c r="E125" s="5" t="n">
+        <v>-0.9910679999999999</v>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-1.129953</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -7239,27 +6807,25 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees 11,134 10,356 38,523</t>
+          <t>LOSS PER SHARE - BASIC $ (0.00) $ (0.00) $</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.03605</v>
+      <c r="E126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="127">
@@ -7270,27 +6836,25 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Travel 29,005 5,470 67,458</t>
+          <t>LOSS PER SHARE – DILUTED $ (0.00) $ (0.00) $</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G127" s="5" t="n">
-        <v>0.09973799999999999</v>
+      <c r="E127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -7301,3298 +6865,26 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>(1,108,597) (903,474) (2,503,239)</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G128" s="5" t="n">
-        <v>-2.400157</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Interest expense (91) (1,843) (3,776)</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" s="5" t="n">
-        <v>-0.005528</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Interest income 33,868 24,225 63,891</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G130" s="5" t="n">
-        <v>0.08909400000000001</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Miscellaneous income - - -</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G131" s="5" t="n">
-        <v>0.000882</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Rental income 3600 6,600 10,800</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" s="5" t="n">
-        <v>0.0198</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Loss on revaluation of deferred compensation liability (752,117) - (986,837)</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Other income realization of flow-through premium liability - 66,590 849,057</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>1.376199</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>LOSS BEFORE INCOME TAXES (1,823,337) (874,492) (2,570,104)</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" s="5" t="n">
-        <v>-1.129953</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>INCOME TAXES - - -</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>TaxProvision</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>LOSS FOR THE PERIOD $ (1,823,337) $ (874,492) $ (2,570,104) $</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" s="5" t="n">
-        <v>-1.129953</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>LOSS PER SHARE - BASIC $ (0.005) $ (0.00) $ (0.007) $</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G138" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>LOSS PER SHARE – DILUTED $ (0.005) $ (0.00) $ (0.007) $</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>COMMON SHARES OUTSTANDING 326,225,863 287,958,552 326,225,863</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
+          <t>COMMON SHARES OUTSTANDING 287,958,552 197,384,423</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
         <is>
           <t>SharesOutstanding</t>
         </is>
       </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" s="5" t="n">
+      <c r="E128" s="5" t="n">
+        <v>197.384423</v>
+      </c>
+      <c r="F128" s="5" t="n">
         <v>277.097878</v>
       </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>For the Three and Nine Months Ended December 31, 2025 and</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G141" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>December 31, December</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G142" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>2025 2024 2025</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G143" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>OPERATING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Net loss for the period $ (1,823,337) $ (874,492) $ (2,570,104) $</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" s="5" t="n">
-        <v>-1.129953</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Amortization 7,878 8,235 23,635</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" s="5" t="n">
-        <v>0.024705</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Flow-through share premium - - (849,057)</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" s="5" t="n">
-        <v>-1.165956</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Loss on revaluation of DSUs to be settled in cash 752,117 - 986,837</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Share-based payments 292,705 338,615 998,395</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G148" s="5" t="n">
-        <v>1.010176</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>(770,637) (527,642) (1,410,294)</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G149" s="5" t="n">
-        <v>-1.261028</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Taxes recoverable (128,249) (31,666) (109,798)</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G150" s="5" t="n">
-        <v>-0.186557</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Other receivables 1,260 (3,780) 1,260</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr"/>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G151" s="5" t="n">
-        <v>-0.00442</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Prepaid expenses 49,552 50,793 (31,919)</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G152" s="5" t="n">
-        <v>0.016269</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Trade and other payables (784,834) (63,860) 208,592</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr"/>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G153" s="5" t="n">
-        <v>0.028921</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Lease liability (9,317) (7,184) (23,683)</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G154" s="5" t="n">
-        <v>-0.02155</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Cash used in operating activities (1,642,225) (583,339) (1,365,842)</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G155" s="5" t="n">
-        <v>-1.428365</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Investment in exploration and evaluation assets (1,962,666) (521,676) (6,188,160)</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G156" s="5" t="n">
-        <v>-3.3988</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Property acquisition costs (285,000) - (285,000)</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr"/>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Reclamation bond - - (3,000)</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr"/>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Cash used in investing activities (2,247,666) (521,676) (6,476,160)</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G159" s="5" t="n">
-        <v>-3.3988</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Proceeds from share issuance - - 10,256,619</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G160" s="5" t="n">
-        <v>7.314428</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Cash provided by financing activities - - 10,256,619</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G161" s="5" t="n">
-        <v>7.314428</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>NET INCREASE IN CASH (3,889,891) (1,105,015) 2,414,617</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G162" s="5" t="n">
-        <v>2.487263</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>CASH AND CASH EQUIVALENTS</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr"/>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>BEGINNING OF THE PERIOD 8,185,511 3,676,936 1,881,003</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G164" s="5" t="n">
-        <v>0.084658</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>CASH AND CASH EQUIVALENTS – END</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>OF THE PERIOD $ 4,295,620 $ 2,571,921 $ 4,295,620 $</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr"/>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G165" s="5" t="n">
-        <v>2.571921</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Cash and cash equivalents 14 $ 2,571,922 $</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr"/>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0.084658</v>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>GST receivable 200,293</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr"/>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>0.013736</v>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Other receivable 8,820</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>0.0044</v>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Prepaid expenses 71,783</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr"/>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>0.08805200000000001</v>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Total Current Assets 2,852,818</t>
-        </is>
-      </c>
-      <c r="D170" t="inlineStr"/>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F170" s="5" t="n">
-        <v>0.190846</v>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>Exploration and evaluation costs 5,6 54,456,281</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F171" s="5" t="n">
-        <v>51.057481</v>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>Right-of-use asset 47,464</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F172" s="5" t="n">
-        <v>0.06780600000000001</v>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>Equipment and camp buildings 7 20,346</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F173" s="5" t="n">
-        <v>0.024711</v>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Total Non-Current Assets 54,524,091</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F174" s="5" t="n">
-        <v>51.149998</v>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Total Assets $ 57,376,909 $</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F175" s="5" t="n">
-        <v>51.340844</v>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Trade and other payables 9 $ 354,135 $</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F176" s="5" t="n">
-        <v>0.507694</v>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Flow-through premium liability -</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr"/>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F177" s="5" t="n">
-        <v>0.314123</v>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Current portion of lease liability 8 28,733</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F178" s="5" t="n">
-        <v>0.028733</v>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Total Current Liabilities 382,868</t>
-        </is>
-      </c>
-      <c r="D179" t="inlineStr"/>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F179" s="5" t="n">
-        <v>0.85055</v>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Lease obligation liability 8 30,084</t>
-        </is>
-      </c>
-      <c r="D180" t="inlineStr"/>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F180" s="5" t="n">
-        <v>0.051634</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Deferred income tax liability 4,011,000</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F181" s="5" t="n">
-        <v>4.011</v>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Total Non-Current Liabilities 4,041,084</t>
-        </is>
-      </c>
-      <c r="D182" t="inlineStr"/>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F182" s="5" t="n">
-        <v>4.062634</v>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Total Liabilities 4,423,952</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr"/>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F183" s="5" t="n">
-        <v>4.913184</v>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Share capital 11 73,110,216</t>
-        </is>
-      </c>
-      <c r="D184" t="inlineStr"/>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F184" s="5" t="n">
-        <v>66.465142</v>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Contributed surplus 11 14,069,402</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F185" s="5" t="n">
-        <v>13.059226</v>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Deficit (34,226,661)</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="n">
-        <v>-33.096708</v>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Total Shareholders' Equity 52,952,957</t>
-        </is>
-      </c>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F187" s="5" t="n">
-        <v>46.42766</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>SHAREHOLDERS' EQUITY</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Total Liabilities and Shareholders' Equity $ 57,376,909 $</t>
-        </is>
-      </c>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F188" s="5" t="n">
-        <v>51.340844</v>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>"Jim Pettit" Director</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>For the Three and Nine Months Ended December 30, 2024 and</t>
-        </is>
-      </c>
-      <c r="D189" t="inlineStr"/>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F189" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>"Jim Pettit" Director</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>2024 2023 2024</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr"/>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F190" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Amortization (Note 7 and 8) $ 8,235 $ 9,016 $ 24,705 $</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F191" s="5" t="n">
-        <v>0.02705</v>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Consulting 25,000 5,000 92,279</t>
-        </is>
-      </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F192" s="5" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B193" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C193" t="inlineStr">
-        <is>
-          <t>Management and personnel (Note 10) 463,671 136,071 743,267</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F193" s="5" t="n">
-        <v>0.419753</v>
-      </c>
-      <c r="G193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
-        <is>
-          <t>Marketing and conferences 23,646 40,143 121,995</t>
-        </is>
-      </c>
-      <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F194" s="5" t="n">
-        <v>0.103433</v>
-      </c>
-      <c r="G194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B195" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C195" t="inlineStr">
-        <is>
-          <t>Office 20,381 26,697 68,227</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F195" s="5" t="n">
-        <v>0.061371</v>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B196" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C196" t="inlineStr">
-        <is>
-          <t>Professional fees 6,500 89,548 192,790</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F196" s="5" t="n">
-        <v>0.097048</v>
-      </c>
-      <c r="G196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B197" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C197" t="inlineStr">
-        <is>
-          <t>Share based payments 338,615 324,958 1,010,176</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F197" s="5" t="n">
-        <v>0.972861</v>
-      </c>
-      <c r="G197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B198" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C198" t="inlineStr">
-        <is>
-          <t>Shareholder communications 1,600 11,147 10,930</t>
-        </is>
-      </c>
-      <c r="D198" t="inlineStr"/>
-      <c r="E198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F198" s="5" t="n">
-        <v>0.023392</v>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B199" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C199" t="inlineStr">
-        <is>
-          <t>Transfer agent and filing fees 10,356 13,940 36,050</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
-      <c r="E199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F199" s="5" t="n">
-        <v>0.04562</v>
-      </c>
-      <c r="G199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B200" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C200" t="inlineStr">
-        <is>
-          <t>Travel 5,470 574 99,738</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
-      <c r="E200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F200" s="5" t="n">
-        <v>0.024789</v>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>(903,474) (657,094) (2,400,157)</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F201" s="5" t="n">
-        <v>-1.805317</v>
-      </c>
-      <c r="G201" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>Interest expense (1,843) (2,853) (5,528)</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr"/>
-      <c r="E202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F202" s="5" t="n">
-        <v>-0.008559000000000001</v>
-      </c>
-      <c r="G202" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>Interest income 24,225 2,499 89,094</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F203" s="5" t="n">
-        <v>0.038362</v>
-      </c>
-      <c r="G203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>Miscellaneous income - - 882</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr"/>
-      <c r="E204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F204" s="5" t="n">
-        <v>0.000135</v>
-      </c>
-      <c r="G204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>Rental income 6,600 6,600 19,800</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
-      <c r="E205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F205" s="5" t="n">
-        <v>0.0198</v>
-      </c>
-      <c r="G205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>Other income realization of flow-through premium liability - 66,590 1,165,956</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
-      <c r="E206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F206" s="5" t="n">
-        <v>1.376199</v>
-      </c>
-      <c r="G206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>OTHER INCOME (EXPENSE)</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>LOSS BEFORE INCOME TAXES (874,492) (584,258) (1,129,953)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F207" s="5" t="n">
-        <v>-0.9910679999999999</v>
-      </c>
-      <c r="G207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>LOSS FOR THE PERIOD $ (874,492) $ (584,258) $ (1,129,953) $</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F208" s="5" t="n">
-        <v>-0.9910679999999999</v>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>LOSS PER SHARE - BASIC $ (0.00) $ (0.00) $ 0.00 $</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F209" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>NET LOSS AND TOTAL COMPREHENSIVE</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>LOSS PER SHARE – DILUTED $ (0.00) $ (0.00) $ 0.00 $</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F210" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G210" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>COMMON SHARES OUTSTANDING 287,958,552 197,384,423 277,097,878</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>SharesOutstanding</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F211" s="5" t="n">
-        <v>197.384423</v>
-      </c>
-      <c r="G211" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>For the Three and Nine Months Ended December 31, 2024 and</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F212" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVERAGE NUMBER OF</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>2024 2023 2024</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F213" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>OPERATING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Net loss for the period $ (874,492) $ (584,258) $ (1,129,953) $</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="n">
-        <v>-0.9910679999999999</v>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Amortization 8,235 9,016 24,705</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F215" s="5" t="n">
-        <v>0.02705</v>
-      </c>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Flow-through share premium - (66,590) (1,165,956)</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr"/>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F216" s="5" t="n">
-        <v>-0.7645110000000001</v>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Share-based payments 338,615 324,958 1,010,176</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr"/>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F217" s="5" t="n">
-        <v>0.972862</v>
-      </c>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>(527,642) (316,874) (1,261,028)</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr"/>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F218" s="5" t="n">
-        <v>-0.755667</v>
-      </c>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Taxes recoverable (31,666) (19,429) (186,557)</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr"/>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F219" s="5" t="n">
-        <v>-0.059097</v>
-      </c>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Other receivables (3,780) - (4,420)</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr"/>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Prepaid expenses 50,793 (18,571) 16,269</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr"/>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F221" s="5" t="n">
-        <v>0.007412</v>
-      </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Trade and other payables (63,860) 45,488 28,921</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F222" s="5" t="n">
-        <v>0.065762</v>
-      </c>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Lease liability (7,184) (5,792) (21,550)</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr"/>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F223" s="5" t="n">
-        <v>-0.017375</v>
-      </c>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Cash used in operating activities (583,339) (315,178) (1,428,365)</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F224" s="5" t="n">
-        <v>-0.758965</v>
-      </c>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Investment in exploration and evaluation assets (521,676) (185,844) (3,398,800)</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F225" s="5" t="n">
-        <v>-1.951175</v>
-      </c>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Property acquisition costs - - -</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr"/>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>INVESTING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Cash used in investing activities (521,676) (185,844) (3,398,800)</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F227" s="5" t="n">
-        <v>-1.951175</v>
-      </c>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Proceeds from share issuance - - 7,314,428</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F228" s="5" t="n">
-        <v>0.168916</v>
-      </c>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Cash provided by financing activities - - 7,314,428</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F229" s="5" t="n">
-        <v>0.168916</v>
-      </c>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>NET INCREASE IN CASH (1,105,015) (501,022) 2,487,263</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F230" s="5" t="n">
-        <v>-2.541224</v>
-      </c>
-      <c r="G230" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>BEGINNING OF THE PERIOD 3,676,936 781,793 84,658</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F231" s="5" t="n">
-        <v>2.821995</v>
-      </c>
-      <c r="G231" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>CASH AND CASH EQUIVALENTS – END</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>OF THE PERIOD $ 2,571,921 $ 280,771 $ 2,571,921 $</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr"/>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F232" s="5" t="n">
-        <v>0.280771</v>
-      </c>
-      <c r="G232" t="inlineStr">
+      <c r="G128" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/SURG.xlsx
+++ b/output/pdf_financials_xlsx/SURG.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/SURG.xlsx
+++ b/output/pdf_financials_xlsx/SURG.xlsx
@@ -573,13 +573,13 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.09137099999999999</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>0.160506</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0</v>
+        <v>0.163074</v>
       </c>
     </row>
     <row r="10">
@@ -589,13 +589,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-1.805317</v>
+        <v>1.805317</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-2.400157</v>
+        <v>2.400157</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>-2.503239</v>
+        <v>2.503239</v>
       </c>
     </row>
     <row r="11">
@@ -643,13 +643,13 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Right-of-use asset 20,341</t>
+          <t>8 Right-of-use asset 20,341</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Right-of-use asset 47,464</t>
+          <t>8 Right-of-use asset 47,464</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5690,7 +5690,11 @@
           <t>Consulting 28,529 25,000</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -5777,7 +5781,11 @@
           <t>Office 29,883 20,381</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr"/>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -5973,13 +5981,13 @@
         </is>
       </c>
       <c r="E98" s="5" t="n">
-        <v>-1.805317</v>
+        <v>1.805317</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>-2.400157</v>
+        <v>2.400157</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-2.503239</v>
+        <v>2.503239</v>
       </c>
     </row>
     <row r="99">
@@ -6395,7 +6403,11 @@
           <t>Consulting 25,000 5,000</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E112" s="5" t="n">
         <v>0.03</v>
       </c>
@@ -6482,7 +6494,11 @@
           <t>Office 20,381 26,697</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E115" s="5" t="n">
         <v>0.061371</v>
       </c>

--- a/output/pdf_financials_xlsx/SURG.xlsx
+++ b/output/pdf_financials_xlsx/SURG.xlsx
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.038362</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.08909400000000001</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.063891</v>
       </c>
     </row>
     <row r="13">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -6719,7 +6719,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E122" s="5" t="n">

--- a/output/pdf_financials_xlsx/SURG.xlsx
+++ b/output/pdf_financials_xlsx/SURG.xlsx
@@ -5026,7 +5026,11 @@
           <t>Proceeds from share issuance - -</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
         <v>0.168916</v>
       </c>
